--- a/curriculum.xlsx
+++ b/curriculum.xlsx
@@ -685,7 +685,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,12 +708,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFD095"/>
-        <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -848,7 +842,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -965,15 +959,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1002,7 +992,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFAFD095"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -5424,21 +5414,21 @@
       </c>
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
       <c r="N7" s="18" t="s">
         <v>169</v>
       </c>
       <c r="O7" s="18"/>
       <c r="P7" s="18"/>
-      <c r="Q7" s="28" t="s">
+      <c r="Q7" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="18"/>
       <c r="T7" s="26" t="s">
         <v>171</v>
       </c>
@@ -5479,11 +5469,11 @@
       <c r="Q8" s="17"/>
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
-      <c r="T8" s="29" t="s">
+      <c r="T8" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
       <c r="W8" s="17"/>
       <c r="X8" s="17"/>
       <c r="Y8" s="17"/>
@@ -5620,54 +5610,54 @@
       <c r="AB12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31" t="s">
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31" t="s">
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31" t="s">
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31" t="s">
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31" t="s">
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31" t="s">
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31" t="s">
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31" t="s">
+      <c r="X13" s="30"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="31"/>
+      <c r="AA13" s="30"/>
+      <c r="AB13" s="30"/>
     </row>
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14"/>

--- a/curriculum.xlsx
+++ b/curriculum.xlsx
@@ -5434,11 +5434,11 @@
       </c>
       <c r="U7" s="26"/>
       <c r="V7" s="26"/>
-      <c r="W7" s="28" t="s">
+      <c r="W7" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="28"/>
+      <c r="X7" s="18"/>
+      <c r="Y7" s="18"/>
       <c r="Z7" s="18" t="s">
         <v>156</v>
       </c>

--- a/curriculum.xlsx
+++ b/curriculum.xlsx
@@ -5414,11 +5414,11 @@
       </c>
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
-      <c r="K7" s="28" t="s">
+      <c r="K7" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
       <c r="N7" s="18" t="s">
         <v>169</v>
       </c>

--- a/curriculum.xlsx
+++ b/curriculum.xlsx
@@ -594,7 +594,7 @@
   </si>
   <si>
     <t xml:space="preserve">Quiz
-Friday 11 Sept 19:00</t>
+Friday 25 Sept 19:00</t>
   </si>
   <si>
     <t xml:space="preserve">EXAMS</t>
